--- a/out/Attention_Base_repeat_5_000006.xlsx
+++ b/out/Attention_Base_repeat_5_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.556325642217417e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08438480768506497</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1689297339021736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0194880177913958</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06475166442322568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2444321660704994</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5541030433219986</v>
+        <v>-5.457359611755237e-06</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0467694028973443</v>
+        <v>-0.001071493806572021</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4028526571241431</v>
+        <v>-0.001076951166183804</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08192082715885056</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5199482700256048</v>
+        <v>-0.001083146413859446</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04486282609988666</v>
+        <v>0.0001602529436927853</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.527682525776231</v>
+        <v>-0.0006328427302956115</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01852900052948198</v>
+        <v>-0.0001183258851303577</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5198305874830726</v>
+        <v>-0.001219558839837671</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02308603502812542</v>
+        <v>0.001166263563820836</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5474763734630048</v>
+        <v>0.001299112481750199</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01389973439154032</v>
+        <v>0.0007958667334778528</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5521757733858368</v>
+        <v>0.001723438622434973</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01056623891274916</v>
+        <v>0.0007257076889717144</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5594043808195763</v>
+        <v>0.002378553598775994</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004670697256883739</v>
+        <v>0.000304112929646637</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5581718723189736</v>
+        <v>0.00226154567700834</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003705173577296268</v>
+        <v>0.0002745677110139979</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5609111095432001</v>
+        <v>0.002507379531749175</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001836089473792515</v>
+        <v>0.0001333948416604358</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5608732506654687</v>
+        <v>0.002499367545932764</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001065585874391671</v>
+        <v>7.909271455507484e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.561167360520143</v>
+        <v>0.002522002695549396</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005302929371958355</v>
+        <v>3.704635727753742e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5611616940443013</v>
+        <v>0.002516941118977033</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002594676309391166</v>
+        <v>1.451010040579961e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5611499993118744</v>
+        <v>0.002511324374235119</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>6.607068664983939e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5611874566156971</v>
+        <v>0.002510479874586454</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>-1.407830995369688e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5611314695106868</v>
+        <v>0.002499939202203998</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.970370261998147e-05</v>
+        <v>-3.190094464385708e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5611267567002347</v>
+        <v>0.002494977890016045</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>-2.989689481548246e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5611241460540584</v>
+        <v>0.002490376115653314</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5611186804883393</v>
+        <v>0.002490300008641789</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5611152958698885</v>
+        <v>0.002490839676541975</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5611096284396148</v>
+        <v>0.002490507573218784</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611100089746726</v>
+        <v>0.002490888108276529</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5611102372957072</v>
+        <v>0.002491116429311224</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5611103272403571</v>
+        <v>0.002491206373961293</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5611094693067723</v>
+        <v>0.00249034844037646</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.561109697627807</v>
+        <v>0.002490576761411038</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5611089019635953</v>
+        <v>0.002489781097199302</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5611089642329684</v>
+        <v>0.002489843366572401</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5611089919082453</v>
+        <v>0.002489871041849372</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5611091441222685</v>
+        <v>0.002490023255872424</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5611087981813068</v>
+        <v>0.002489677314910805</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611088742883185</v>
+        <v>0.002489753421922447</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.56110904033998</v>
+        <v>0.002489919473584043</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611094001185801</v>
+        <v>0.002490279252184089</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611094208750378</v>
+        <v>0.002490300008641789</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611095246573263</v>
+        <v>0.002490403790930286</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.561109752978361</v>
+        <v>0.00249063211196498</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611096284396148</v>
+        <v>0.002490507573218784</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611096561148916</v>
+        <v>0.002490535248495638</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611097114654455</v>
+        <v>0.002490590599049581</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611099743805763</v>
+        <v>0.002490853514180402</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>1.958776160273009</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611098913547455</v>
+        <v>0.002490770488349604</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611096837901687</v>
+        <v>0.00249056292377261</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.561109697627807</v>
+        <v>0.002490576761411038</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611098360041917</v>
+        <v>0.002490715137795778</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611095523326032</v>
+        <v>0.002490431466207258</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611093793621224</v>
+        <v>0.00249025849572639</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611092755798339</v>
+        <v>0.002490154713437893</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611094208750378</v>
+        <v>0.002490300008641789</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.561109663033711</v>
+        <v>0.00249054216731491</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>1.358776160273009</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611094900632301</v>
+        <v>0.002490369196834159</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.561109192554003</v>
+        <v>0.002490071687607094</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5611091787163646</v>
+        <v>0.002490057849968667</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611088120189454</v>
+        <v>0.002489691152549349</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611088120189454</v>
+        <v>0.002489691152549349</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611087497495723</v>
+        <v>0.00248962888317625</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611086459672837</v>
+        <v>0.002489525100887753</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.561108472996803</v>
+        <v>0.002489352130406886</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611085214285375</v>
+        <v>0.002489400562141556</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611081616499375</v>
+        <v>0.002489040783541393</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611081201370222</v>
+        <v>0.002488999270625995</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611081754875759</v>
+        <v>0.002489054621179937</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611082308381298</v>
+        <v>0.002489109971733764</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611082723510452</v>
+        <v>0.002489151484649163</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.561108002517095</v>
+        <v>0.00248888165069907</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611080578676491</v>
+        <v>0.002488937001252896</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611082031628529</v>
+        <v>0.002489082296456792</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611081685687567</v>
+        <v>0.002489047702360666</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611081547311181</v>
+        <v>0.002489033864722238</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611082446757683</v>
+        <v>0.002489123809372191</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611085629414529</v>
+        <v>0.002489442075056955</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611083830521528</v>
+        <v>0.002489262185756932</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611084245650683</v>
+        <v>0.002489303698672331</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.561108237756949</v>
+        <v>0.002489116890553036</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611083069451414</v>
+        <v>0.00248918607874529</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611081062993836</v>
+        <v>0.002488985432987567</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.561108147812299</v>
+        <v>0.002489026945902966</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.873712549958921e-06</v>
+        <v>-4.309598161615673e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-1.481593977180774</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611081754875759</v>
+        <v>0.002489054621179937</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_5_000006.xlsx
+++ b/out/Attention_Base_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>-6.556325642217417e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.08438480768506497</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.1689297339021736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.0194880177913958</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06483122663724702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06475166442322568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2444321660704994</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5541030433219986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0467694028973443</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4028526571241431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.08192082715885056</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5199482700256048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.04486282609988666</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.527682525776231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01852900052948198</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5198305874830726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02308603502812542</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5474763734630048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01389973439154032</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5521757733858368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01056623891274916</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5594043808195763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.004670697256883739</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5581718723189736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.003705173577296268</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5609111095432001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001836089473792515</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5608732506654687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001065585874391671</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.561167360520143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0005302929371958355</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5611616940443013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0002594676309391166</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5611499993118744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001485320277835259</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5611874566156971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>4.633531262135388e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5611314695106868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.970370261998147e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5611267567002347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.677176780651038e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5611241460540584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5611186804883393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5611152958698885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5611096284396148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5611100089746726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5611102372957072</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5611103272403571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5611094693067723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.561109697627807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5611089019635953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5611089642329684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5611089919082453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5611091441222685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5611087981813068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611088742883185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.56110904033998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611094001185801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611094208750378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611095246573263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.561109752978361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611096284396148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611096561148916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611097114654455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611099743805763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611098913547455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611096837901687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.561109697627807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611098360041917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611095523326032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611093793621224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611092755798339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611094208750378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.561109663033711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611094900632301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.561109192554003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5611091787163646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611088120189454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611088120189454</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611087497495723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611086459672837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.561108472996803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611085214285375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611081616499375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611081201370222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611081754875759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611082308381298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611082723510452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.561108002517095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611080578676491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611082031628529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611081685687567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611081547311181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611082446757683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611085629414529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611083830521528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611084245650683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.561108237756949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611083069451414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611081062993836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.561108147812299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.873712549958921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611081754875759</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_5_000006.xlsx
+++ b/out/Attention_Base_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.001602170988917351</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.001958003267645836</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.003214017022401094</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.005272951908409595</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.00516072940081358</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0050325533375144</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.003932016901671886</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.004222501534968615</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.004986858926713467</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.00492548244073987</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.004239775706082582</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.003320144489407539</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.003327739890664816</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.002804096322506666</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.002260949462652206</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.001703145913779736</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001450946554541588</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.001507215667515993</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.002085521351546049</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.002221495378762484</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.002136752009391785</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001784356310963631</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.00155002111569047</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.001747967675328255</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.001620037481188774</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.002068583853542805</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.00325068412348628</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.003815704956650734</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.004089116584509611</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.004323395900428295</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.004243198782205582</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.004013724159449339</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.003869806881994009</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.004302205052226782</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.004606258124113083</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.004729737062007189</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.005021511111408472</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.005102415569126606</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.005127687472850084</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.005364987067878246</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.005859999917447567</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.00657104654237628</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0075880978256464</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.008636406622827053</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.009259186685085297</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.009788260795176029</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01057536154985428</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>-1.572706125420518e-05</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.0483169334537267</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0110560217872262</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.09671435015372233</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.00924483870115754</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01169937290251255</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.06681670935983816</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.01619342928458149</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01254782639443874</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.08996313684407575</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.008866366249509762</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01325886324048042</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.09149022721617087</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.003659054835664152</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01387106627225876</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.08993453340209276</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.004559387025061533</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01480282563716173</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.09539572624475672</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>0.002743335502610705</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0162360668182373</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.09632073378365487</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>0.002084454598152154</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01725530624389648</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.09774598404177814</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>0.0009199679821571501</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01891284249722958</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.09749819371384895</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>0.0007289636376568415</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.01982984505593777</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>0.09803588659381936</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>0.0003577146381792318</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.01951412111520767</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>0.09802439228128665</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>0.0002073716544309565</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.02379107102751732</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.09807872657311079</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>9.973122684266348e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.02788351289927959</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.0980735961756634</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>4.674366692287064e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.02938098646700382</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.0980672517426142</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>2.503887500112463e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.03014933690428734</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.09807102216729405</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.03010246530175209</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.09805493801403116</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.03026306256651878</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.09805000155201671</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.03108539059758186</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.09804560042341171</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.03134539723396301</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.03212406486272812</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.09804098490273906</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.03269696980714798</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.03417674452066422</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.09804103333447362</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.03554751724004745</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.0980412616555083</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.03399736434221268</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.09804135160015826</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.03250616788864136</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.09804049366657343</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.03177811950445175</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.03035964258015156</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.09803992632339639</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.03129132091999054</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.09803998859276948</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.03118900395929813</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.09804001626804634</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.03099635988473892</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.09804016848206963</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.03090727888047695</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.09803982254110789</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.03088542819023132</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.09803989864811953</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.03121850453317165</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.09804006469978113</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.03121794760227203</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.09804042447838117</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.03159915283322334</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.03225651383399963</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.09804054901712737</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.03360747918486595</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.09804077733816206</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.03339338302612305</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.09804065279941587</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.03340617194771767</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.09804068047469272</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.03280766308307648</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>0.09804073582524667</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.03338040411472321</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>0.09804099874037737</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.03279237449169159</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>0.09804091571454657</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.03269529342651367</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>0.0980407081499698</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.03271161019802094</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>0.09804072198760812</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.03256144374608994</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>0.09804086036399286</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.0314893051981926</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>0.09804057669240422</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.03093235194683075</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>0.09804040372192348</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.03016488254070282</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>0.09804029993963498</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.03083936870098114</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>0.09804044523483887</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.03127467259764671</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>0.09804068739351211</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.03014285489916801</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>0.09804051442303113</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.02947025373578072</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>0.09804021691380418</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.02841491624712944</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>0.09804020307616564</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.02779841609299183</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.02763453125953674</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>0.09803983637874643</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.02658684179186821</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>0.09803977410937334</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.02682948485016823</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>0.09803967032708484</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.02631836570799351</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>0.09803949735660408</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02573519200086594</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>0.09803954578833864</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.02500803209841251</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>0.0980391860097386</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.02490672469139099</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>0.09803914449682319</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.02466126345098019</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.02492249570786953</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>0.09803925519793084</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.02455195412039757</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>0.09803929671084624</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.02389715425670147</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>0.09803902687689615</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.02389714494347572</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>0.0980390822274501</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.0239497609436512</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>0.098039227522654</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.02372287586331367</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>0.09803919292855776</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.0234899278730154</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>0.09803917909091921</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.02327212691307068</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>0.09803926903556939</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.02320022508502007</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>0.09803958730125403</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.023660808801651</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>0.0980394074119539</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02345256693661213</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>0.09803944892486929</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.02320663072168827</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>0.09803926211675</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.02337388694286346</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>0.0980393313049425</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.02273343876004219</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>0.09803913065918465</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.02286535687744617</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3299999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>0.09803917217210005</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.02275359444320202</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>0.09803919984737691</v>
       </c>
     </row>
   </sheetData>
